--- a/util/Analysis/BadSmells/ShotgunSurgery/ShotgunSurgerySmellRelationAnalysisOfscikit-learn.xlsx
+++ b/util/Analysis/BadSmells/ShotgunSurgery/ShotgunSurgerySmellRelationAnalysisOfscikit-learn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Documents/workspace/DissertationProject/util/Analysis/BadSmells/ShotgunSurgery/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Documents/PycharmProjects/DissertationProject/util/Analysis/BadSmells/ShotgunSurgery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{0CA76947-3411-744D-A75F-2395995992B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7164A3-201A-2942-851C-EE6DBE504120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14000"/>
+    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShotgunSurgerySmellRelationAnal" sheetId="1" r:id="rId1"/>
@@ -1588,7 +1588,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2422,7 +2422,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I722"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -2455,7 +2456,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2484,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2513,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2542,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2571,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2600,7 +2601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2629,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2658,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2716,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -2774,7 +2775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -2832,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2890,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -2919,7 +2920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2948,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2977,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -3006,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -3064,7 +3065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -3093,7 +3094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -3122,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -3151,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -3180,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -3209,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -3238,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -3267,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -3296,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -3354,7 +3355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -3383,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -3412,7 +3413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3441,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -3470,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -3499,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -3528,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -3586,7 +3587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -3760,7 +3761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -3789,7 +3790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -3934,7 +3935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -3963,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -3992,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -4050,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -4079,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -4108,7 +4109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -4746,7 +4747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -4775,7 +4776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -4804,7 +4805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -4833,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>81</v>
       </c>
@@ -4862,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>82</v>
       </c>
@@ -4891,7 +4892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -4920,7 +4921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>84</v>
       </c>
@@ -4949,7 +4950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -4978,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>86</v>
       </c>
@@ -5007,7 +5008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>87</v>
       </c>
@@ -7095,7 +7096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>133</v>
       </c>
@@ -7124,7 +7125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>134</v>
       </c>
@@ -7153,7 +7154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>135</v>
       </c>
@@ -7182,7 +7183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>135</v>
       </c>
@@ -7211,7 +7212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>136</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>137</v>
       </c>
@@ -7269,7 +7270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>138</v>
       </c>
@@ -7298,7 +7299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>139</v>
       </c>
@@ -7327,7 +7328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>63</v>
       </c>
@@ -7356,7 +7357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>140</v>
       </c>
@@ -7385,7 +7386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>141</v>
       </c>
@@ -7414,7 +7415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>142</v>
       </c>
@@ -7443,7 +7444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>143</v>
       </c>
@@ -7472,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>144</v>
       </c>
@@ -7501,7 +7502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>145</v>
       </c>
@@ -7530,7 +7531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>146</v>
       </c>
@@ -7559,7 +7560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>147</v>
       </c>
@@ -7588,7 +7589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>148</v>
       </c>
@@ -7617,7 +7618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>149</v>
       </c>
@@ -7646,7 +7647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>150</v>
       </c>
@@ -7675,7 +7676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>150</v>
       </c>
@@ -7704,7 +7705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>151</v>
       </c>
@@ -7733,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>33</v>
       </c>
@@ -7762,7 +7763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>152</v>
       </c>
@@ -7791,7 +7792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>153</v>
       </c>
@@ -7820,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>154</v>
       </c>
@@ -7849,7 +7850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>155</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>156</v>
       </c>
@@ -7907,7 +7908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>157</v>
       </c>
@@ -7936,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>158</v>
       </c>
@@ -7965,7 +7966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -7994,7 +7995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>159</v>
       </c>
@@ -8023,7 +8024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>37</v>
       </c>
@@ -8052,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>160</v>
       </c>
@@ -8081,7 +8082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>161</v>
       </c>
@@ -8110,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>162</v>
       </c>
@@ -8139,7 +8140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>163</v>
       </c>
@@ -8168,7 +8169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>164</v>
       </c>
@@ -8777,7 +8778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>146</v>
       </c>
@@ -8806,7 +8807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>184</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>185</v>
       </c>
@@ -8864,7 +8865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>186</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>187</v>
       </c>
@@ -8922,7 +8923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>49</v>
       </c>
@@ -8951,7 +8952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>188</v>
       </c>
@@ -8980,7 +8981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>189</v>
       </c>
@@ -9009,7 +9010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>190</v>
       </c>
@@ -9038,7 +9039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>50</v>
       </c>
@@ -10575,7 +10576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>85</v>
       </c>
@@ -10604,7 +10605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>86</v>
       </c>
@@ -10633,7 +10634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>87</v>
       </c>
@@ -13243,7 +13244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>282</v>
       </c>
@@ -13272,7 +13273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>283</v>
       </c>
@@ -13301,7 +13302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>101</v>
       </c>
@@ -13330,7 +13331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>48</v>
       </c>
@@ -13359,7 +13360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>284</v>
       </c>
@@ -13388,7 +13389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>285</v>
       </c>
@@ -14345,7 +14346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>81</v>
       </c>
@@ -14374,7 +14375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>82</v>
       </c>
@@ -14403,7 +14404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>83</v>
       </c>
@@ -14432,7 +14433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>321</v>
       </c>
@@ -14461,7 +14462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>321</v>
       </c>
@@ -14490,7 +14491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>322</v>
       </c>
@@ -14519,7 +14520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>323</v>
       </c>
@@ -14548,7 +14549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>324</v>
       </c>
@@ -14577,7 +14578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>325</v>
       </c>
@@ -14606,7 +14607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>326</v>
       </c>
@@ -14635,7 +14636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>326</v>
       </c>
@@ -14664,7 +14665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>18</v>
       </c>
@@ -14693,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>327</v>
       </c>
@@ -14722,7 +14723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>328</v>
       </c>
@@ -14751,7 +14752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>329</v>
       </c>
@@ -14780,7 +14781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>330</v>
       </c>
@@ -15012,7 +15013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>339</v>
       </c>
@@ -15041,7 +15042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>340</v>
       </c>
@@ -15070,7 +15071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>341</v>
       </c>
@@ -15099,7 +15100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>342</v>
       </c>
@@ -15128,7 +15129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>343</v>
       </c>
@@ -15157,7 +15158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>344</v>
       </c>
@@ -15186,7 +15187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>345</v>
       </c>
@@ -15215,7 +15216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>346</v>
       </c>
@@ -15244,7 +15245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>187</v>
       </c>
@@ -15273,7 +15274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>32</v>
       </c>
@@ -15302,7 +15303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>81</v>
       </c>
@@ -15331,7 +15332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>82</v>
       </c>
@@ -15360,7 +15361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>83</v>
       </c>
@@ -15389,7 +15390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>94</v>
       </c>
@@ -15418,7 +15419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>95</v>
       </c>
@@ -15447,7 +15448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>96</v>
       </c>
@@ -15476,7 +15477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>59</v>
       </c>
@@ -15505,7 +15506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>60</v>
       </c>
@@ -15563,7 +15564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>350</v>
       </c>
@@ -17013,7 +17014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>81</v>
       </c>
@@ -17042,7 +17043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>82</v>
       </c>
@@ -17071,7 +17072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>83</v>
       </c>
@@ -17100,7 +17101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>372</v>
       </c>
@@ -17129,7 +17130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>111</v>
       </c>
@@ -17158,7 +17159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>247</v>
       </c>
@@ -17187,7 +17188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>161</v>
       </c>
@@ -17216,7 +17217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>373</v>
       </c>
@@ -17245,7 +17246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>374</v>
       </c>
@@ -17274,7 +17275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>250</v>
       </c>
@@ -17303,7 +17304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>375</v>
       </c>
@@ -17332,7 +17333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>376</v>
       </c>
@@ -17361,7 +17362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>274</v>
       </c>
@@ -17390,7 +17391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>274</v>
       </c>
@@ -17419,7 +17420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>274</v>
       </c>
@@ -17448,7 +17449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>275</v>
       </c>
@@ -17477,7 +17478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>275</v>
       </c>
@@ -17506,7 +17507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>377</v>
       </c>
@@ -17535,7 +17536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>378</v>
       </c>
@@ -17564,7 +17565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>379</v>
       </c>
@@ -17593,7 +17594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>380</v>
       </c>
@@ -17622,7 +17623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>280</v>
       </c>
@@ -17651,7 +17652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>381</v>
       </c>
@@ -17680,7 +17681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>382</v>
       </c>
@@ -17709,7 +17710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>382</v>
       </c>
@@ -17738,7 +17739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>383</v>
       </c>
@@ -17767,7 +17768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>384</v>
       </c>
@@ -17796,7 +17797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>385</v>
       </c>
@@ -17825,7 +17826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>386</v>
       </c>
@@ -17854,7 +17855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>386</v>
       </c>
@@ -17883,7 +17884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>386</v>
       </c>
@@ -17912,7 +17913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>168</v>
       </c>
@@ -17941,7 +17942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>168</v>
       </c>
@@ -17970,7 +17971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>387</v>
       </c>
@@ -17999,7 +18000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>388</v>
       </c>
@@ -18028,7 +18029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>389</v>
       </c>
@@ -18057,7 +18058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>170</v>
       </c>
@@ -18086,7 +18087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>390</v>
       </c>
@@ -18115,7 +18116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>391</v>
       </c>
@@ -18144,7 +18145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>392</v>
       </c>
@@ -18927,7 +18928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>410</v>
       </c>
@@ -18956,7 +18957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>141</v>
       </c>
@@ -18985,7 +18986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>411</v>
       </c>
@@ -19014,7 +19015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>406</v>
       </c>
@@ -19043,7 +19044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>412</v>
       </c>
@@ -19072,7 +19073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>413</v>
       </c>
@@ -19101,7 +19102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>413</v>
       </c>
@@ -19130,7 +19131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>414</v>
       </c>
@@ -19159,7 +19160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>415</v>
       </c>
@@ -19188,7 +19189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>416</v>
       </c>
@@ -19217,7 +19218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>416</v>
       </c>
@@ -19246,7 +19247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>362</v>
       </c>
@@ -19275,7 +19276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>417</v>
       </c>
@@ -19304,7 +19305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>418</v>
       </c>
@@ -19333,7 +19334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>418</v>
       </c>
@@ -19391,7 +19392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>422</v>
       </c>
@@ -19420,7 +19421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>423</v>
       </c>
@@ -19449,7 +19450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>341</v>
       </c>
@@ -19942,7 +19943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>94</v>
       </c>
@@ -19971,7 +19972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>95</v>
       </c>
@@ -20000,7 +20001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>96</v>
       </c>
@@ -20029,7 +20030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>59</v>
       </c>
@@ -20058,7 +20059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>60</v>
       </c>
@@ -20087,7 +20088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>438</v>
       </c>
@@ -20116,7 +20117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>136</v>
       </c>
@@ -20145,7 +20146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>412</v>
       </c>
@@ -20174,7 +20175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>412</v>
       </c>
@@ -20203,7 +20204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>48</v>
       </c>
@@ -20232,7 +20233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>439</v>
       </c>
@@ -20261,7 +20262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>440</v>
       </c>
@@ -20290,7 +20291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>440</v>
       </c>
@@ -20319,7 +20320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>324</v>
       </c>
@@ -20348,7 +20349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>324</v>
       </c>
@@ -20377,7 +20378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>325</v>
       </c>
@@ -20406,7 +20407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>441</v>
       </c>
@@ -20435,7 +20436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>442</v>
       </c>
@@ -20464,7 +20465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>443</v>
       </c>
@@ -20493,7 +20494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>444</v>
       </c>
@@ -20522,7 +20523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>445</v>
       </c>
@@ -20551,7 +20552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>445</v>
       </c>
@@ -20580,7 +20581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>446</v>
       </c>
@@ -21102,7 +21103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>462</v>
       </c>
@@ -21131,7 +21132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>53</v>
       </c>
@@ -21247,7 +21248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>326</v>
       </c>
@@ -21276,7 +21277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>30</v>
       </c>
@@ -21305,7 +21306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>30</v>
       </c>
@@ -21334,7 +21335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>31</v>
       </c>
@@ -21363,7 +21364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>468</v>
       </c>
@@ -21392,7 +21393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>469</v>
       </c>
@@ -21421,7 +21422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>470</v>
       </c>
@@ -21450,7 +21451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>471</v>
       </c>
@@ -21595,7 +21596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>475</v>
       </c>
@@ -21624,7 +21625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
         <v>475</v>
       </c>
@@ -21653,7 +21654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>164</v>
       </c>
@@ -21682,7 +21683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>164</v>
       </c>
@@ -21711,7 +21712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>164</v>
       </c>
@@ -21740,7 +21741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>476</v>
       </c>
@@ -21769,7 +21770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>476</v>
       </c>
@@ -21798,7 +21799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>18</v>
       </c>
@@ -21827,7 +21828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>18</v>
       </c>
@@ -21856,7 +21857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>18</v>
       </c>
@@ -21885,7 +21886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>18</v>
       </c>
@@ -21914,7 +21915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>18</v>
       </c>
@@ -21943,7 +21944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>477</v>
       </c>
@@ -21972,7 +21973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>478</v>
       </c>
@@ -22001,7 +22002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>479</v>
       </c>
@@ -22030,7 +22031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>480</v>
       </c>
@@ -22059,7 +22060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>481</v>
       </c>
@@ -22088,7 +22089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>482</v>
       </c>
@@ -22436,7 +22437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>49</v>
       </c>
@@ -23219,7 +23220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>321</v>
       </c>
@@ -23335,7 +23336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
         <v>32</v>
       </c>
@@ -23365,7 +23366,18 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I722"/>
+  <autoFilter ref="A1:I722" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="1"/>
+        <filter val="2"/>
+        <filter val="3"/>
+        <filter val="4"/>
+        <filter val="5"/>
+        <filter val="71"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>